--- a/甘特图_智检哨兵.xlsx
+++ b/甘特图_智检哨兵.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12790"/>
+    <workbookView windowWidth="22170" windowHeight="12200"/>
   </bookViews>
   <sheets>
     <sheet name="GanttChart" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="142">
   <si>
     <t>智检哨兵：自主巡防与多模式人机协同</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>巡检模式：6700 事件/截图</t>
+  </si>
+  <si>
+    <t>王才睿+郑浩然+张经纬</t>
   </si>
   <si>
     <t>2.3</t>
@@ -3384,7 +3387,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="100" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D12" s="101">
         <v>46211</v>
@@ -3461,10 +3464,10 @@
     </row>
     <row r="13" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:66">
       <c r="A13" s="98" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" s="99" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="100" t="s">
         <v>24</v>
@@ -3544,10 +3547,10 @@
     </row>
     <row r="14" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:66">
       <c r="A14" s="98" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="99" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="100"/>
       <c r="D14" s="120"/>
@@ -3615,13 +3618,13 @@
     </row>
     <row r="15" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:66">
       <c r="A15" s="98" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" s="114" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="100" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="122">
         <v>46210</v>
@@ -3697,13 +3700,13 @@
     </row>
     <row r="16" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:66">
       <c r="A16" s="98" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="99" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" s="100" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="101">
         <v>46211</v>
@@ -3780,13 +3783,13 @@
     </row>
     <row r="17" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A17" s="98" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="99" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="100" t="s">
         <v>37</v>
-      </c>
-      <c r="B17" s="99" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="100" t="s">
-        <v>36</v>
       </c>
       <c r="D17" s="101">
         <v>46211</v>
@@ -3863,13 +3866,13 @@
     </row>
     <row r="18" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A18" s="98" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="99" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="100" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D18" s="101">
         <v>46212</v>
@@ -3946,10 +3949,10 @@
     </row>
     <row r="19" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A19" s="98" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="99" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19" s="100"/>
       <c r="D19" s="101"/>
@@ -4017,13 +4020,13 @@
     </row>
     <row r="20" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A20" s="98" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B20" s="114" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="100" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" s="125">
         <v>46210</v>
@@ -4100,13 +4103,13 @@
     </row>
     <row r="21" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A21" s="98" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21" s="99" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" s="100" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21" s="101">
         <v>46213</v>
@@ -4183,13 +4186,13 @@
     </row>
     <row r="22" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A22" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="99" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22" s="100" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22" s="101">
         <v>46214</v>
@@ -4266,10 +4269,10 @@
     </row>
     <row r="23" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A23" s="98" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" s="99" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C23" s="100"/>
       <c r="D23" s="101"/>
@@ -4337,13 +4340,13 @@
     </row>
     <row r="24" s="38" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A24" s="98" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" s="99" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C24" s="100" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D24" s="101">
         <v>46214</v>
@@ -4420,13 +4423,13 @@
     </row>
     <row r="25" s="39" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A25" s="128" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25" s="129" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C25" s="130" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" s="131">
         <v>46214</v>
@@ -4503,13 +4506,13 @@
     </row>
     <row r="26" s="40" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A26" s="128" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" s="129" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C26" s="130" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D26" s="131">
         <v>46215</v>
@@ -4586,10 +4589,10 @@
     </row>
     <row r="27" s="39" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A27" s="135" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="129" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C27" s="136"/>
       <c r="D27" s="137"/>
@@ -4657,13 +4660,13 @@
     </row>
     <row r="28" s="41" customFormat="1" ht="27" customHeight="1" spans="1:65">
       <c r="A28" s="141" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B28" s="142" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C28" s="142" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D28" s="143">
         <v>46216</v>
@@ -4740,10 +4743,10 @@
     </row>
     <row r="29" s="39" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A29" s="145" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" s="146" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C29" s="146" t="s">
         <v>17</v>
@@ -4823,13 +4826,13 @@
     </row>
     <row r="30" s="39" customFormat="1" ht="17.5" customHeight="1" spans="1:65">
       <c r="A30" s="145" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B30" s="146" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30" s="146" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D30" s="147">
         <v>46215</v>
@@ -5155,7 +5158,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98a45887-8bda-4ece-9189-d3733d450bd1}</x14:id>
+          <x14:id>{b9cafb66-5c9e-489d-8fe2-7d9764206cf5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5188,7 +5191,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{98a45887-8bda-4ece-9189-d3733d450bd1}">
+          <x14:cfRule type="dataBar" id="{b9cafb66-5c9e-489d-8fe2-7d9764206cf5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5221,13 +5224,13 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" ht="14" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B2" s="4"/>
     </row>
@@ -5236,39 +5239,39 @@
     </row>
     <row r="4" ht="17.5" customHeight="1" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" s="6"/>
     </row>
     <row r="5" ht="56" customHeight="1" spans="1:4">
       <c r="B5" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:4">
       <c r="B7" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1" spans="1:4">
       <c r="B9" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:4">
       <c r="B11" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" ht="17.5" customHeight="1" spans="1:4">
       <c r="A13" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" ht="17.5" customHeight="1" spans="1:4">
       <c r="A15" s="10"/>
       <c r="B15" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -5276,7 +5279,7 @@
     <row r="16" ht="17.5" customHeight="1" spans="1:4">
       <c r="A16" s="10"/>
       <c r="B16" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
@@ -5284,31 +5287,31 @@
     <row r="17" ht="17.5" customHeight="1" spans="1:2">
       <c r="A17" s="13"/>
       <c r="B17" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.5" customHeight="1" spans="1:2">
       <c r="A18" s="13"/>
       <c r="B18" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2">
       <c r="A19" s="13"/>
       <c r="B19" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="17.5" customHeight="1" spans="1:2">
       <c r="A20" s="13"/>
       <c r="B20" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" ht="17.5" customHeight="1" spans="1:2">
       <c r="A21" s="13"/>
       <c r="B21" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" ht="17.5" customHeight="1" spans="1:2">
@@ -5317,13 +5320,13 @@
     </row>
     <row r="23" ht="17.5" customHeight="1" spans="1:2">
       <c r="A23" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:2">
       <c r="A24" s="13"/>
       <c r="B24" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" ht="17.5" customHeight="1" spans="1:2">
@@ -5333,19 +5336,19 @@
     <row r="26" ht="17.5" customHeight="1" spans="1:2">
       <c r="A26" s="13"/>
       <c r="B26" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="17.5" customHeight="1" spans="1:2">
       <c r="A27" s="13"/>
       <c r="B27" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:2">
       <c r="A28" s="13"/>
       <c r="B28" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" ht="17.5" customHeight="1" spans="1:2">
@@ -5355,19 +5358,19 @@
     <row r="30" ht="17.5" customHeight="1" spans="1:2">
       <c r="A30" s="13"/>
       <c r="B30" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" ht="17.5" customHeight="1" spans="1:2">
       <c r="A31" s="13"/>
       <c r="B31" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" ht="17.5" customHeight="1" spans="1:2">
       <c r="A32" s="13"/>
       <c r="B32" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" ht="17.5" customHeight="1" spans="1:2">
@@ -5377,13 +5380,13 @@
     <row r="34" ht="28" customHeight="1" spans="1:2">
       <c r="A34" s="13"/>
       <c r="B34" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" ht="17.5" customHeight="1" spans="1:2">
       <c r="A35" s="13"/>
       <c r="B35" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" ht="17.5" customHeight="1" spans="1:2">
@@ -5392,27 +5395,27 @@
     </row>
     <row r="37" ht="17.5" customHeight="1" spans="1:2">
       <c r="A37" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:2">
       <c r="B38" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1" spans="1:2">
       <c r="B40" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:2">
       <c r="B42" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1" spans="1:2">
       <c r="B44" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5420,101 +5423,101 @@
     </row>
     <row r="46" ht="28" customHeight="1" spans="1:2">
       <c r="B46" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" ht="17.5" customHeight="1" spans="1:2">
       <c r="A48" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1" spans="1:2">
       <c r="B49" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1" spans="1:2">
       <c r="A51" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1" spans="1:2">
       <c r="A52" s="19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1" spans="1:2">
       <c r="A53" s="19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1" spans="1:2">
       <c r="A54" s="8"/>
       <c r="B54" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:2">
       <c r="A55" s="8"/>
       <c r="B55" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1" spans="1:2">
       <c r="A56" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1" spans="1:2">
       <c r="A57" s="8"/>
       <c r="B57" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1" spans="1:2">
       <c r="A58" s="8"/>
       <c r="B58" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1" spans="1:2">
       <c r="A59" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1" spans="1:2">
       <c r="A60" s="8"/>
       <c r="B60" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1" spans="1:2">
       <c r="A61" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1" spans="1:2">
       <c r="A62" s="20"/>
       <c r="B62" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -5522,31 +5525,31 @@
     </row>
     <row r="64" ht="17.5" customHeight="1" spans="1:2">
       <c r="A64" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1" spans="1:2">
       <c r="B65" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="67" ht="17.5" customHeight="1" spans="1:2">
       <c r="A67" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1" spans="1:2">
       <c r="A68" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:2">
       <c r="A69" s="20"/>
       <c r="B69" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1" spans="1:2">
@@ -5555,16 +5558,16 @@
     </row>
     <row r="71" ht="14" customHeight="1" spans="1:2">
       <c r="A71" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1" spans="1:2">
       <c r="A72" s="20"/>
       <c r="B72" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1" spans="1:2">
@@ -5573,16 +5576,16 @@
     </row>
     <row r="74" ht="14" customHeight="1" spans="1:2">
       <c r="A74" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="75" ht="42" customHeight="1" spans="1:2">
       <c r="A75" s="20"/>
       <c r="B75" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1" spans="1:2">
@@ -5591,16 +5594,16 @@
     </row>
     <row r="77" ht="14" customHeight="1" spans="1:2">
       <c r="A77" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="78" ht="28" customHeight="1" spans="1:2">
       <c r="A78" s="20"/>
       <c r="B78" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1" spans="1:2">
@@ -5609,28 +5612,28 @@
     </row>
     <row r="80" ht="14" customHeight="1" spans="1:2">
       <c r="A80" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1" spans="1:2">
       <c r="A81" s="20"/>
       <c r="B81" s="27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="82" ht="14" customHeight="1" spans="1:2">
       <c r="A82" s="20"/>
       <c r="B82" s="27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="83" ht="14" customHeight="1" spans="1:2">
       <c r="A83" s="20"/>
       <c r="B83" s="27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1" spans="1:2">
@@ -5639,28 +5642,28 @@
     </row>
     <row r="85" ht="14" customHeight="1" spans="1:2">
       <c r="A85" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1" spans="1:2">
       <c r="A86" s="20"/>
       <c r="B86" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1" spans="1:2">
       <c r="A87" s="20"/>
       <c r="B87" s="165" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1" spans="1:2">
       <c r="A88" s="20"/>
       <c r="B88" s="166" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="89" ht="14" customHeight="1" spans="1:2">
@@ -5669,21 +5672,21 @@
     </row>
     <row r="90" ht="14" customHeight="1" spans="1:2">
       <c r="A90" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91" ht="28" customHeight="1" spans="1:2">
       <c r="A91" s="8"/>
       <c r="B91" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/甘特图_智检哨兵.xlsx
+++ b/甘特图_智检哨兵.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22170" windowHeight="12200"/>
+    <workbookView windowWidth="24750" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="GanttChart" sheetId="1" r:id="rId1"/>
@@ -2370,8 +2370,8 @@
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.81818181818182" style="43" customWidth="1"/>
-    <col min="2" max="2" width="35.1727272727273" style="44" customWidth="1"/>
-    <col min="3" max="3" width="11.8545454545455" style="44" customWidth="1"/>
+    <col min="2" max="2" width="29.8181818181818" style="44" customWidth="1"/>
+    <col min="3" max="3" width="18.3636363636364" style="44" customWidth="1"/>
     <col min="4" max="5" width="17" style="45" customWidth="1"/>
     <col min="6" max="6" width="6" style="44" customWidth="1"/>
     <col min="7" max="7" width="6.72727272727273" style="44" customWidth="1"/>
@@ -5158,7 +5158,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b9cafb66-5c9e-489d-8fe2-7d9764206cf5}</x14:id>
+          <x14:id>{176e82c3-8aa4-4abf-aa52-9a1992cc8101}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5191,7 +5191,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b9cafb66-5c9e-489d-8fe2-7d9764206cf5}">
+          <x14:cfRule type="dataBar" id="{176e82c3-8aa4-4abf-aa52-9a1992cc8101}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
